--- a/inventory_schema.xlsx
+++ b/inventory_schema.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Stock_mgmt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6592E146-75C5-4B23-84B3-D759012ECBBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C8369E-4B13-47BE-AB5A-E1013D6D7E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{3D656413-42AF-4A82-845E-B1F04302D92D}"/>
+    <workbookView xWindow="0" yWindow="12" windowWidth="23256" windowHeight="14616" xr2:uid="{3D656413-42AF-4A82-845E-B1F04302D92D}"/>
   </bookViews>
   <sheets>
     <sheet name="Stock_statement" sheetId="4" r:id="rId1"/>
@@ -992,7 +992,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="4"/>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1298,9 +1298,18 @@
   <dimension ref="A1:M27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="42.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2676,5 +2685,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>